--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484604_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484604_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5547</v>
+        <v>4.2114</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3993</v>
+        <v>3.1056</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1554</v>
+        <v>1.1058</v>
       </c>
       <c r="G2" t="n">
         <v>-0.6067</v>
@@ -610,13 +610,13 @@
         <v>4.2149</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6849</v>
+        <v>1.3416</v>
       </c>
       <c r="T2" t="n">
-        <v>4.2836</v>
+        <v>1.9898</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5987</v>
+        <v>-0.6482</v>
       </c>
       <c r="V2" t="n">
         <v>1.2774</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3755</v>
+        <v>3.318</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6846</v>
+        <v>0.6024</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6908</v>
+        <v>2.7156</v>
       </c>
       <c r="G3" t="n">
         <v>-0.8235</v>
@@ -688,13 +688,13 @@
         <v>3.4819</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1153</v>
+        <v>1.0579</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2436</v>
+        <v>1.1614</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1283</v>
+        <v>-0.1035</v>
       </c>
       <c r="V3" t="n">
         <v>2.5339</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6497000000000001</v>
+        <v>1.9111</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0055</v>
+        <v>0.1073</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6552</v>
+        <v>1.8038</v>
       </c>
       <c r="G5" t="n">
         <v>-0.1064</v>
@@ -844,13 +844,13 @@
         <v>3.2986</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9823</v>
+        <v>0.279</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4593</v>
+        <v>0.6535</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5231</v>
+        <v>-0.3744</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6439</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. BAENA SÁNCHEZ</t>
+          <t>P. BAENA SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3251</v>
+        <v>0.5374</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3251</v>
+        <v>0.5982</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.0608</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3251</v>
+        <v>-1.7376</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3251</v>
+        <v>-0.9559</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.7817</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3251</v>
+        <v>-1.0673</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3251</v>
+        <v>0.1951</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.2624</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.6703</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-1.151</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.4807</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.1465</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.2598</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.4063</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0012</v>
+        <v>0.5313</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2917</v>
+        <v>-1.4123</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2904</v>
+        <v>1.9436</v>
       </c>
       <c r="G7" t="n">
         <v>-4.8732</v>
@@ -1000,13 +1000,13 @@
         <v>3.4819</v>
       </c>
       <c r="S7" t="n">
-        <v>0.228</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0935</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3215</v>
+        <v>-0.0253</v>
       </c>
       <c r="V7" t="n">
         <v>3.1778</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BERMEJO DORRONSORO</t>
+          <t>P. BAENA SÁNCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4086</v>
+        <v>0.3251</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.553</v>
+        <v>0.3251</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1445</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4721</v>
+        <v>0.3251</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6194</v>
+        <v>0.3251</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1473</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5661</v>
+        <v>0.3251</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4828</v>
+        <v>0.3251</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0833</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0382</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1021</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1094</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0196</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0898</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0104</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.0104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. FAS MONROS</t>
+          <t>I. DE LA IGLESIA SANTAMARIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4566</v>
+        <v>0.0804</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7511</v>
+        <v>0.7175</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2945</v>
+        <v>-0.6371</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6014</v>
+        <v>1.1693</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7296</v>
+        <v>-0.2762</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1282</v>
+        <v>1.4456</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.641</v>
+        <v>1.2687</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.641</v>
+        <v>0.5603</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.7085</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0397</v>
+        <v>-0.0994</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0885</v>
+        <v>-0.8365</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1282</v>
+        <v>0.7371</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3665</v>
+        <v>2.0158</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3665</v>
+        <v>2.9321</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2218</v>
+        <v>0.3846</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1101</v>
+        <v>0.365</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1117</v>
+        <v>0.0196</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-3.4894</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-3.4894</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. BAENA SANCHEZ</t>
+          <t>R. FAS MONROS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5564</v>
+        <v>-0.4319</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3222</v>
+        <v>-0.7511</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2342</v>
+        <v>0.3193</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7376</v>
+        <v>-0.6014</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9559</v>
+        <v>-0.7296</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7817</v>
+        <v>0.1282</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0673</v>
+        <v>-0.641</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1951</v>
+        <v>-0.641</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2624</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6703</v>
+        <v>0.0397</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.151</v>
+        <v>-0.0885</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4807</v>
+        <v>0.1282</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4661</v>
+        <v>0.3665</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6493</v>
+        <v>0.3665</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2403</v>
+        <v>-0.197</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6606</v>
+        <v>-0.1101</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5797</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. DE LA IGLESIA SANTAMARIA</t>
+          <t>J. BERMEJO DORRONSORO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6448</v>
+        <v>-0.6974</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1068</v>
+        <v>-0.5941</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.538</v>
+        <v>-0.1033</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1693</v>
+        <v>-0.4721</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2762</v>
+        <v>-0.6194</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4456</v>
+        <v>0.1473</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2687</v>
+        <v>0.5661</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5603</v>
+        <v>0.4828</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7085</v>
+        <v>0.0833</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0994</v>
+        <v>-1.0382</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8365</v>
+        <v>-1.1021</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7371</v>
+        <v>0.064</v>
       </c>
       <c r="P11" t="n">
-        <v>2.0158</v>
+        <v>0.1833</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9321</v>
+        <v>1.2828</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3406</v>
+        <v>-0.3982</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4593</v>
+        <v>-0.0607</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1187</v>
+        <v>-0.3375</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.4894</v>
+        <v>-0.0104</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.4894</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. FRANCH RUIZ</t>
+          <t>M. REOS CAMPOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.731</v>
+        <v>-1.1209</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6032</v>
+        <v>-1.9785</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1278</v>
+        <v>0.8576</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1408</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9037</v>
+        <v>-0.6885</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7629</v>
+        <v>0.1699</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5286</v>
+        <v>-0.491</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1954</v>
+        <v>0.1084</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6667999999999999</v>
+        <v>-0.5994</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6122</v>
+        <v>-0.0276</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7083</v>
+        <v>-0.7968</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0961</v>
+        <v>0.7692</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1833</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R12" t="n">
         <v>1.0995</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2266</v>
+        <v>-0.22</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8416</v>
+        <v>-0.0056</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6151</v>
+        <v>-0.2144</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. REOS CAMPOS</t>
+          <t>I. FRANCH RUIZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.2478</v>
+        <v>-1.2554</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8824</v>
+        <v>-1.2763</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.0209</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-1.1408</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6885</v>
+        <v>-1.9037</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1699</v>
+        <v>0.7629</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.491</v>
+        <v>-0.5286</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1084</v>
+        <v>-1.1954</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5994</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0276</v>
+        <v>-0.6122</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7968</v>
+        <v>-0.7083</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7692</v>
+        <v>0.0961</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.6493</v>
+        <v>0.1833</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R13" t="n">
         <v>1.0995</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3468</v>
+        <v>-0.2979</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0905</v>
+        <v>0.1686</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4373</v>
+        <v>-0.4664</v>
       </c>
       <c r="V13" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,28 +1501,28 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.109300000000001</v>
+        <v>9.659800000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1438</v>
+        <v>1.6945</v>
       </c>
       <c r="F14" t="n">
-        <v>7.965399999999998</v>
+        <v>7.9654</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.1352</v>
+        <v>-7.135199999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8855000000000003</v>
+        <v>-0.8855000000000006</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.2496</v>
+        <v>-6.249600000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.2029</v>
+        <v>-1.202900000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>9.052200000000001</v>
+        <v>9.052199999999999</v>
       </c>
       <c r="L14" t="n">
         <v>-10.2551</v>
@@ -1531,7 +1531,7 @@
         <v>-5.932099999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.937299999999997</v>
+        <v>-9.937299999999999</v>
       </c>
       <c r="O14" t="n">
         <v>4.0053</v>
@@ -1546,13 +1546,13 @@
         <v>22.907</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0136</v>
+        <v>2.5641</v>
       </c>
       <c r="T14" t="n">
-        <v>4.656899999999999</v>
+        <v>5.2075</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.6435</v>
+        <v>-2.6433</v>
       </c>
       <c r="V14" t="n">
         <v>5.0678</v>
@@ -1561,7 +1561,7 @@
         <v>11.4339</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.3661</v>
+        <v>-6.366099999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.6627</v>
+        <v>6.1548</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0944</v>
+        <v>4.6521</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5683</v>
+        <v>1.5027</v>
       </c>
       <c r="G15" t="n">
         <v>3.2924</v>
@@ -1624,13 +1624,13 @@
         <v>1.8326</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8562</v>
+        <v>0.3482</v>
       </c>
       <c r="T15" t="n">
-        <v>2.178</v>
+        <v>0.7357</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3218</v>
+        <v>-0.3875</v>
       </c>
       <c r="V15" t="n">
         <v>2.1476</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. ASSARDO JOVANI</t>
+          <t>I. EGIDO MUNOZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5586</v>
+        <v>4.1247</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4524</v>
+        <v>2.5707</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8938</v>
+        <v>1.554</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3418</v>
+        <v>2.7066</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4635</v>
+        <v>0.7097</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8783</v>
+        <v>1.9969</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5452</v>
+        <v>2.2856</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8269</v>
+        <v>1.6348</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7183</v>
+        <v>0.6509</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2033</v>
+        <v>0.421</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3633</v>
+        <v>-0.925</v>
       </c>
       <c r="O16" t="n">
-        <v>0.16</v>
+        <v>1.346</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9163</v>
+        <v>0.733</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9163</v>
+        <v>1.8326</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.5175</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2738</v>
+        <v>0.1177</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3398</v>
+        <v>-0.6352</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6335</v>
+        <v>1.2026</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6335</v>
+        <v>1.267</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.267</v>
+        <v>-0.0644</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. EGIDO MUNOZ</t>
+          <t>L. ASSARDO JOVANI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3948</v>
+        <v>3.7072</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9938</v>
+        <v>4.4524</v>
       </c>
       <c r="F17" t="n">
-        <v>1.401</v>
+        <v>-0.7452</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7066</v>
+        <v>3.3418</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7097</v>
+        <v>2.4635</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9969</v>
+        <v>0.8783</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2856</v>
+        <v>3.5452</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6348</v>
+        <v>2.8269</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6509</v>
+        <v>0.7183</v>
       </c>
       <c r="M17" t="n">
-        <v>0.421</v>
+        <v>-0.2033</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.925</v>
+        <v>-0.3633</v>
       </c>
       <c r="O17" t="n">
-        <v>1.346</v>
+        <v>0.16</v>
       </c>
       <c r="P17" t="n">
-        <v>0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8326</v>
+        <v>0.9163</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2474</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4593</v>
+        <v>0.2738</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7882</v>
+        <v>-0.1912</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2026</v>
+        <v>-0.6335</v>
       </c>
       <c r="W17" t="n">
-        <v>1.267</v>
+        <v>0.6335</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.0644</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="18">
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. LARIO ECHEVARRIAS</t>
+          <t>A. GUTIERREZ MARCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1075</v>
+        <v>0.2879</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.6368</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1984</v>
+        <v>0.9248</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.06320000000000001</v>
+        <v>1.6516</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1932</v>
+        <v>1.6325</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2564</v>
+        <v>0.0191</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0742</v>
+        <v>1.5664</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7153</v>
+        <v>2.1241</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.641</v>
+        <v>-0.5577</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1374</v>
+        <v>0.0852</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.522</v>
+        <v>-0.4916</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3846</v>
+        <v>0.5768</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3665</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3665</v>
+        <v>0.9163</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1959</v>
+        <v>-0.1646</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1652</v>
+        <v>-0.0878</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0307</v>
+        <v>-0.0767</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GUTIERREZ MARCO</t>
+          <t>P. LARIO ECHEVARRIAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0184</v>
+        <v>0.2575</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.733</v>
+        <v>0.0052</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7513</v>
+        <v>0.2523</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6516</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6325</v>
+        <v>0.1932</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0191</v>
+        <v>-0.2564</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5664</v>
+        <v>0.0742</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1241</v>
+        <v>0.7153</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5577</v>
+        <v>-0.641</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0852</v>
+        <v>-0.1374</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4916</v>
+        <v>-0.522</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5768</v>
+        <v>0.3846</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8326</v>
+        <v>0.3665</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9163</v>
+        <v>0.3665</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4342</v>
+        <v>-0.0458</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.184</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2502</v>
+        <v>0.0232</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3828</v>
+        <v>-1.9341</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9638</v>
+        <v>-0.7715</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.419</v>
+        <v>-1.1626</v>
       </c>
       <c r="G22" t="n">
         <v>1.0486</v>
@@ -2170,13 +2170,13 @@
         <v>1.4661</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8974</v>
+        <v>-0.4487</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1448</v>
+        <v>0.3371</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0423</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-2.5339</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. ALVAREZ LABRADOR</t>
+          <t>J. ESTARLICH MARTINEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7645</v>
+        <v>-2.128</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8517</v>
+        <v>-1.8914</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9128</v>
+        <v>-0.2366</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6401</v>
+        <v>-0.1723</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2329</v>
+        <v>0.0106</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4072</v>
+        <v>-0.1829</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2118</v>
+        <v>-0.0483</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8111</v>
+        <v>0.5511</v>
       </c>
       <c r="L23" t="n">
         <v>-0.5994</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8519</v>
+        <v>-0.124</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.044</v>
+        <v>-0.5404</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1922</v>
+        <v>0.4164</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1833</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.3665</v>
+        <v>-2.0158</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5498</v>
+        <v>1.8326</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4176</v>
+        <v>-0.1192</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.07389999999999999</v>
+        <v>0.1727</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3437</v>
+        <v>-0.2919</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.89</v>
+        <v>-1.6533</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.267</v>
+        <v>-1.6533</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. ESTARLICH MARTINEZ</t>
+          <t>P. ALVAREZ LABRADOR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.874</v>
+        <v>-2.4295</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0837</v>
+        <v>-0.4671</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7903</v>
+        <v>-1.9624</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1723</v>
+        <v>-0.6401</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0106</v>
+        <v>-0.2329</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1829</v>
+        <v>-0.4072</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0483</v>
+        <v>0.2118</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5511</v>
+        <v>0.8111</v>
       </c>
       <c r="L24" t="n">
         <v>-0.5994</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.124</v>
+        <v>-0.8519</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5404</v>
+        <v>-1.044</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4164</v>
+        <v>0.1922</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.1833</v>
+        <v>0.1833</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.0158</v>
+        <v>-0.3665</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8326</v>
+        <v>0.5498</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8652</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0196</v>
+        <v>0.3107</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8456</v>
+        <v>-0.3933</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.6533</v>
+        <v>-1.89</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.6533</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.3408</v>
+        <v>-4.1921</v>
       </c>
       <c r="E25" t="n">
         <v>-6.0883</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7475</v>
+        <v>1.8961</v>
       </c>
       <c r="G25" t="n">
         <v>-3.4379</v>
@@ -2404,13 +2404,13 @@
         <v>1.6493</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2674</v>
+        <v>-0.1188</v>
       </c>
       <c r="T25" t="n">
         <v>0.2549</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5223</v>
+        <v>-0.3737</v>
       </c>
       <c r="V25" t="n">
         <v>2.48</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.1375</v>
+        <v>-4.6931</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.5126</v>
+        <v>-5.3203</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3751</v>
+        <v>0.6272</v>
       </c>
       <c r="G26" t="n">
         <v>-1.9642</v>
@@ -2482,13 +2482,13 @@
         <v>1.4661</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3209</v>
+        <v>0.1235</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4201</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.741</v>
+        <v>-0.4889</v>
       </c>
       <c r="V26" t="n">
         <v>-1.0198</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-7.6521</v>
+        <v>-8.282999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.4826</v>
+        <v>-5.771</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.1695</v>
+        <v>-2.512</v>
       </c>
       <c r="G27" t="n">
         <v>0.0712</v>
@@ -2560,13 +2560,13 @@
         <v>0.9163</v>
       </c>
       <c r="S27" t="n">
-        <v>0.8423</v>
+        <v>0.2113</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2738</v>
+        <v>-0.0147</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5685</v>
+        <v>0.226</v>
       </c>
       <c r="V27" t="n">
         <v>-3.8009</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-9.109299999999999</v>
+        <v>-7.827299999999998</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.965599999999998</v>
+        <v>-7.965599999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.1438</v>
+        <v>0.1382999999999996</v>
       </c>
       <c r="G28" t="n">
         <v>7.134899999999999</v>
@@ -2638,13 +2638,13 @@
         <v>13.7445</v>
       </c>
       <c r="S28" t="n">
-        <v>-2.013599999999999</v>
+        <v>-0.7316</v>
       </c>
       <c r="T28" t="n">
-        <v>2.6434</v>
+        <v>2.6435</v>
       </c>
       <c r="U28" t="n">
-        <v>-4.6571</v>
+        <v>-3.375</v>
       </c>
       <c r="V28" t="n">
         <v>-5.067699999999999</v>
